--- a/mode_docx_gen/pmi_dzt/part/tdif/rmxu2/RMXU2.xlsx
+++ b/mode_docx_gen/pmi_dzt/part/tdif/rmxu2/RMXU2.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="81">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -251,6 +251,18 @@
   </si>
   <si>
     <t>Nsch</t>
+  </si>
+  <si>
+    <t>ПарамСт1</t>
+  </si>
+  <si>
+    <t>Inomterm</t>
+  </si>
+  <si>
+    <t>Номинальный ток терминала стороны 2</t>
+  </si>
+  <si>
+    <t>Iном_термСт2</t>
   </si>
 </sst>
 </file>
@@ -630,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" customWidth="1"/>
@@ -1215,6 +1227,101 @@
       </c>
       <c r="AE6" s="2" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>5</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
